--- a/inputs/inputs_to_load.xlsx
+++ b/inputs/inputs_to_load.xlsx
@@ -1,16 +1,17 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="20414"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="20417"/>
   <workbookPr filterPrivacy="1"/>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8766A0D5-6819-4359-9A30-6CDE62B7B0FC}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F66893B6-18EB-44EF-B1D6-AE9515CB1517}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="23040" windowHeight="7788" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="23040" windowHeight="8076" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="problem_input" sheetId="7" r:id="rId1"/>
     <sheet name="parameters" sheetId="4" r:id="rId2"/>
     <sheet name="scenarios_input" sheetId="5" r:id="rId3"/>
+    <sheet name="ga_parameters" sheetId="8" r:id="rId4"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -22,7 +23,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="93" uniqueCount="72">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="114" uniqueCount="93">
   <si>
     <t>NA</t>
   </si>
@@ -150,6 +151,9 @@
     <t>required for MIP for single_run and combination_run modes</t>
   </si>
   <si>
+    <t>single_run</t>
+  </si>
+  <si>
     <t>initial_value</t>
   </si>
   <si>
@@ -168,13 +172,37 @@
     <t>scenario_rate_change</t>
   </si>
   <si>
+    <t>optimization_mode</t>
+  </si>
+  <si>
+    <t>two_stage_optimization, deterministic_optimal_evaluation</t>
+  </si>
+  <si>
+    <t>folder_to_be_evaluated</t>
+  </si>
+  <si>
+    <t>deterministic_optimal_solution_file</t>
+  </si>
+  <si>
+    <t>start_solution_file</t>
+  </si>
+  <si>
+    <t>experiment_mode</t>
+  </si>
+  <si>
+    <t>required any time (single_run, scenario_run, scenario_increasing_deviation_run, combination_run)</t>
+  </si>
+  <si>
+    <t>min_scenario_number</t>
+  </si>
+  <si>
     <t>required for scenario_run</t>
   </si>
   <si>
     <t>max_scenario_number</t>
   </si>
   <si>
-    <t>min_scenario_number</t>
+    <t>step_size_scenario_number</t>
   </si>
   <si>
     <t>min_scenario_rate</t>
@@ -183,18 +211,15 @@
     <t>max_scenario_rate</t>
   </si>
   <si>
-    <t>required any time (single_run, scenario_run, scenario_increasing_deviation_run, combination_run)</t>
-  </si>
-  <si>
     <t>increasing_deviation_min_scenario_number</t>
   </si>
   <si>
+    <t>required for scenario_increasing_deviation_run</t>
+  </si>
+  <si>
     <t>increasing_deviation_max_scenario_number</t>
   </si>
   <si>
-    <t>step_size_scenario_number</t>
-  </si>
-  <si>
     <t>increasing_deviation_step_size_scenario_number</t>
   </si>
   <si>
@@ -207,37 +232,76 @@
     <t>increasing_deviation_step_size_rate</t>
   </si>
   <si>
-    <t>deterministic_optimal_solution_file</t>
-  </si>
-  <si>
-    <t>optimization_mode</t>
-  </si>
-  <si>
-    <t>folder_to_be_evaluated</t>
-  </si>
-  <si>
-    <t>required for scenario_increasing_deviation_run</t>
-  </si>
-  <si>
-    <t>two_stage_optimization, deterministic_optimal_evaluation</t>
-  </si>
-  <si>
-    <t>experiment_mode</t>
-  </si>
-  <si>
-    <t>start_solution_file</t>
-  </si>
-  <si>
-    <t>single_run_25_nodes_2024_09_25_15_52</t>
-  </si>
-  <si>
-    <t>single_run_25_nodes_2024_09_25_15_52.xlsx</t>
-  </si>
-  <si>
     <t>two_stage_optimization</t>
   </si>
   <si>
-    <t>scenario_increasing_deviation_run</t>
+    <t>solution_method</t>
+  </si>
+  <si>
+    <t>seed</t>
+  </si>
+  <si>
+    <t>pop_size</t>
+  </si>
+  <si>
+    <t>max_generations</t>
+  </si>
+  <si>
+    <t>time_limit_sec</t>
+  </si>
+  <si>
+    <t>coverage_ratio</t>
+  </si>
+  <si>
+    <t>p_cross</t>
+  </si>
+  <si>
+    <t>p_mut_swap</t>
+  </si>
+  <si>
+    <t>p_mut_add</t>
+  </si>
+  <si>
+    <t>p_mut_remove</t>
+  </si>
+  <si>
+    <t>RNG seed</t>
+  </si>
+  <si>
+    <t>population size</t>
+  </si>
+  <si>
+    <t>number of generations</t>
+  </si>
+  <si>
+    <t>wall-clock time cap (seconds)</t>
+  </si>
+  <si>
+    <t>initial fraction of J* to visit</t>
+  </si>
+  <si>
+    <t>crossover prob</t>
+  </si>
+  <si>
+    <t>swap mutation prob</t>
+  </si>
+  <si>
+    <t>add-node mutation prob</t>
+  </si>
+  <si>
+    <t>remove-node mutation prob</t>
+  </si>
+  <si>
+    <t>heuristic_seed_ratio</t>
+  </si>
+  <si>
+    <t>elite_ratio</t>
+  </si>
+  <si>
+    <t>stall_ratio</t>
+  </si>
+  <si>
+    <t>mip</t>
   </si>
 </sst>
 </file>
@@ -279,6 +343,12 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor theme="2" tint="-9.9978637043366805E-2"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor theme="9" tint="0.79998168889431442"/>
         <bgColor indexed="64"/>
       </patternFill>
@@ -286,12 +356,6 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor theme="7" tint="0.79998168889431442"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="2" tint="-9.9978637043366805E-2"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -308,7 +372,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="12">
+  <cellXfs count="13">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="right"/>
@@ -316,20 +380,23 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="2" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1"/>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="4" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="4" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -620,7 +687,7 @@
     <col min="5" max="5" width="21.109375" style="1" bestFit="1" customWidth="1"/>
     <col min="6" max="6" width="19.77734375" style="1" bestFit="1" customWidth="1"/>
     <col min="7" max="7" width="10.6640625" style="1" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="18.109375" style="1" customWidth="1"/>
+    <col min="8" max="8" width="15.77734375" style="1" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:8" x14ac:dyDescent="0.3">
@@ -634,16 +701,16 @@
         <v>3</v>
       </c>
       <c r="D1" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="E1" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="F1" t="s">
         <v>9</v>
       </c>
       <c r="G1" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="H1" s="1" t="s">
         <v>10</v>
@@ -663,10 +730,10 @@
         <v>40</v>
       </c>
       <c r="E2" s="1">
-        <v>2.2400000000000002</v>
+        <v>1.1200000000000001</v>
       </c>
       <c r="F2" s="1">
-        <v>3.68</v>
+        <v>1.84</v>
       </c>
       <c r="G2" s="1">
         <v>6</v>
@@ -689,10 +756,10 @@
         <v>40</v>
       </c>
       <c r="E3" s="1">
-        <v>2.2400000000000002</v>
+        <v>1.1200000000000001</v>
       </c>
       <c r="F3" s="1">
-        <v>3.68</v>
+        <v>1.84</v>
       </c>
       <c r="G3" s="1">
         <v>0</v>
@@ -712,16 +779,16 @@
         <v>2.5</v>
       </c>
       <c r="D4" s="1">
-        <v>0</v>
+        <v>40</v>
       </c>
       <c r="E4" s="1">
-        <v>0</v>
+        <v>1.1200000000000001</v>
       </c>
       <c r="F4" s="1">
-        <v>3.68</v>
+        <v>1.84</v>
       </c>
       <c r="G4" s="1">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="H4" s="1" t="s">
         <v>16</v>
@@ -741,10 +808,10 @@
         <v>40</v>
       </c>
       <c r="E5" s="1">
-        <v>2.2400000000000002</v>
+        <v>1.1200000000000001</v>
       </c>
       <c r="F5" s="1">
-        <v>3.68</v>
+        <v>1.84</v>
       </c>
       <c r="G5" s="1">
         <v>1</v>
@@ -793,10 +860,10 @@
         <v>80</v>
       </c>
       <c r="E7" s="1">
-        <v>5.12</v>
+        <v>2.56</v>
       </c>
       <c r="F7" s="1">
-        <v>2.96</v>
+        <v>1.48</v>
       </c>
       <c r="G7" s="1">
         <v>0</v>
@@ -819,10 +886,10 @@
         <v>80</v>
       </c>
       <c r="E8" s="1">
-        <v>5.12</v>
+        <v>2.56</v>
       </c>
       <c r="F8" s="1">
-        <v>2.96</v>
+        <v>1.48</v>
       </c>
       <c r="G8" s="1">
         <v>0</v>
@@ -845,10 +912,10 @@
         <v>80</v>
       </c>
       <c r="E9" s="1">
-        <v>5.12</v>
+        <v>2.56</v>
       </c>
       <c r="F9" s="1">
-        <v>2.96</v>
+        <v>1.48</v>
       </c>
       <c r="G9" s="1">
         <v>0</v>
@@ -871,10 +938,10 @@
         <v>80</v>
       </c>
       <c r="E10" s="1">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="F10" s="1">
-        <v>1.52</v>
+        <v>0.76</v>
       </c>
       <c r="G10" s="1">
         <v>0</v>
@@ -897,10 +964,10 @@
         <v>80</v>
       </c>
       <c r="E11" s="1">
-        <v>6.56</v>
+        <v>3.28</v>
       </c>
       <c r="F11" s="1">
-        <v>2.2400000000000002</v>
+        <v>1.1200000000000001</v>
       </c>
       <c r="G11" s="1">
         <v>1</v>
@@ -926,7 +993,7 @@
         <v>0</v>
       </c>
       <c r="F12" s="1">
-        <v>2.2400000000000002</v>
+        <v>1.1200000000000001</v>
       </c>
       <c r="G12" s="1">
         <v>4</v>
@@ -949,10 +1016,10 @@
         <v>100</v>
       </c>
       <c r="E13" s="1">
-        <v>6.56</v>
+        <v>3.28</v>
       </c>
       <c r="F13" s="1">
-        <v>2.2400000000000002</v>
+        <v>1.1200000000000001</v>
       </c>
       <c r="G13" s="1">
         <v>0</v>
@@ -971,17 +1038,17 @@
       <c r="C14" s="1">
         <v>2.5</v>
       </c>
-      <c r="D14" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="E14" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="F14" s="1" t="s">
-        <v>0</v>
+      <c r="D14" s="1">
+        <v>80</v>
+      </c>
+      <c r="E14" s="1">
+        <v>2.56</v>
+      </c>
+      <c r="F14" s="1">
+        <v>1.48</v>
       </c>
       <c r="G14" s="1">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="H14" s="1" t="s">
         <v>19</v>
@@ -1001,10 +1068,10 @@
         <v>100</v>
       </c>
       <c r="E15" s="1">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="F15" s="1">
-        <v>1.52</v>
+        <v>0.76</v>
       </c>
       <c r="G15" s="1">
         <v>0</v>
@@ -1027,10 +1094,10 @@
         <v>40</v>
       </c>
       <c r="E16" s="1">
-        <v>6.56</v>
+        <v>3.28</v>
       </c>
       <c r="F16" s="1">
-        <v>2.2400000000000002</v>
+        <v>1.1200000000000001</v>
       </c>
       <c r="G16" s="1">
         <v>1</v>
@@ -1053,10 +1120,10 @@
         <v>60</v>
       </c>
       <c r="E17" s="1">
-        <v>6.56</v>
+        <v>3.28</v>
       </c>
       <c r="F17" s="1">
-        <v>2.2400000000000002</v>
+        <v>1.1200000000000001</v>
       </c>
       <c r="G17" s="1">
         <v>0</v>
@@ -1079,10 +1146,10 @@
         <v>100</v>
       </c>
       <c r="E18" s="1">
-        <v>6.56</v>
+        <v>3.28</v>
       </c>
       <c r="F18" s="1">
-        <v>2.2400000000000002</v>
+        <v>1.1200000000000001</v>
       </c>
       <c r="G18" s="1">
         <v>0</v>
@@ -1105,10 +1172,10 @@
         <v>100</v>
       </c>
       <c r="E19" s="1">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="F19" s="1">
-        <v>1.52</v>
+        <v>0.76</v>
       </c>
       <c r="G19" s="1">
         <v>0</v>
@@ -1131,10 +1198,10 @@
         <v>100</v>
       </c>
       <c r="E20" s="1">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="F20" s="1">
-        <v>1.52</v>
+        <v>0.76</v>
       </c>
       <c r="G20" s="1">
         <v>0</v>
@@ -1160,7 +1227,7 @@
         <v>0</v>
       </c>
       <c r="F21" s="1">
-        <v>2.2400000000000002</v>
+        <v>1.1200000000000001</v>
       </c>
       <c r="G21" s="1">
         <v>4</v>
@@ -1209,10 +1276,10 @@
         <v>60</v>
       </c>
       <c r="E23" s="1">
-        <v>5.12</v>
+        <v>2.56</v>
       </c>
       <c r="F23" s="1">
-        <v>2.96</v>
+        <v>1.48</v>
       </c>
       <c r="G23" s="1">
         <v>0</v>
@@ -1238,7 +1305,7 @@
         <v>0</v>
       </c>
       <c r="F24" s="1">
-        <v>2.96</v>
+        <v>1.48</v>
       </c>
       <c r="G24" s="1">
         <v>4</v>
@@ -1261,10 +1328,10 @@
         <v>40</v>
       </c>
       <c r="E25" s="1">
-        <v>5.12</v>
+        <v>2.56</v>
       </c>
       <c r="F25" s="1">
-        <v>2.96</v>
+        <v>1.48</v>
       </c>
       <c r="G25" s="1">
         <v>1</v>
@@ -1287,10 +1354,10 @@
         <v>40</v>
       </c>
       <c r="E26" s="1">
-        <v>6.56</v>
+        <v>3.28</v>
       </c>
       <c r="F26" s="1">
-        <v>2.2400000000000002</v>
+        <v>1.1200000000000001</v>
       </c>
       <c r="G26" s="1">
         <v>1</v>
@@ -1306,12 +1373,12 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A72994A6-A966-4EE5-993D-09F1DE73FA00}">
-  <dimension ref="A1:C23"/>
+  <dimension ref="A1:C24"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="45.109375" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="42.33203125" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="83.109375" customWidth="1"/>
+    <col min="1" max="1" width="23.88671875" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="39" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="54.44140625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:3" x14ac:dyDescent="0.3">
@@ -1329,7 +1396,7 @@
       <c r="A2" t="s">
         <v>12</v>
       </c>
-      <c r="B2" s="7">
+      <c r="B2" s="5">
         <v>25</v>
       </c>
       <c r="C2" t="s">
@@ -1340,7 +1407,7 @@
       <c r="A3" t="s">
         <v>4</v>
       </c>
-      <c r="B3" s="7">
+      <c r="B3" s="5">
         <v>5</v>
       </c>
       <c r="C3" t="s">
@@ -1351,7 +1418,7 @@
       <c r="A4" t="s">
         <v>13</v>
       </c>
-      <c r="B4" s="7">
+      <c r="B4" s="5">
         <v>1</v>
       </c>
       <c r="C4" t="s">
@@ -1362,7 +1429,7 @@
       <c r="A5" t="s">
         <v>5</v>
       </c>
-      <c r="B5" s="7">
+      <c r="B5" s="5">
         <v>2</v>
       </c>
       <c r="C5" t="s">
@@ -1373,7 +1440,7 @@
       <c r="A6" t="s">
         <v>6</v>
       </c>
-      <c r="B6" s="7">
+      <c r="B6" s="5">
         <v>35</v>
       </c>
       <c r="C6" t="s">
@@ -1384,7 +1451,7 @@
       <c r="A7" t="s">
         <v>11</v>
       </c>
-      <c r="B7" s="7">
+      <c r="B7" s="5">
         <v>24</v>
       </c>
       <c r="C7" t="s">
@@ -1392,171 +1459,175 @@
       </c>
     </row>
     <row r="8" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A8" s="10" t="s">
+      <c r="A8" t="s">
+        <v>70</v>
+      </c>
+      <c r="B8" s="5" t="s">
+        <v>92</v>
+      </c>
+    </row>
+    <row r="9" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A9" s="6" t="s">
+        <v>49</v>
+      </c>
+      <c r="B9" s="7" t="s">
+        <v>69</v>
+      </c>
+      <c r="C9" s="6" t="s">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="10" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A10" s="6" t="s">
+        <v>51</v>
+      </c>
+      <c r="B10" s="7"/>
+      <c r="C10" s="6"/>
+    </row>
+    <row r="11" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A11" s="6" t="s">
+        <v>52</v>
+      </c>
+      <c r="B11" s="7"/>
+      <c r="C11" s="6"/>
+    </row>
+    <row r="12" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A12" s="6" t="s">
+        <v>53</v>
+      </c>
+      <c r="B12" s="7"/>
+      <c r="C12" s="6"/>
+    </row>
+    <row r="13" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A13" s="6" t="s">
+        <v>54</v>
+      </c>
+      <c r="B13" s="7" t="s">
+        <v>42</v>
+      </c>
+      <c r="C13" s="6" t="s">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="14" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A14" s="8" t="s">
+        <v>56</v>
+      </c>
+      <c r="B14" s="9">
+        <v>1</v>
+      </c>
+      <c r="C14" s="8" t="s">
+        <v>57</v>
+      </c>
+    </row>
+    <row r="15" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A15" s="8" t="s">
+        <v>58</v>
+      </c>
+      <c r="B15" s="9">
+        <v>13</v>
+      </c>
+      <c r="C15" s="8" t="s">
+        <v>57</v>
+      </c>
+    </row>
+    <row r="16" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A16" s="8" t="s">
+        <v>59</v>
+      </c>
+      <c r="B16" s="9">
+        <v>2</v>
+      </c>
+      <c r="C16" s="8" t="s">
+        <v>57</v>
+      </c>
+    </row>
+    <row r="17" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A17" s="8" t="s">
+        <v>60</v>
+      </c>
+      <c r="B17" s="9">
+        <v>-0.35</v>
+      </c>
+      <c r="C17" s="8" t="s">
+        <v>57</v>
+      </c>
+    </row>
+    <row r="18" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A18" s="8" t="s">
+        <v>61</v>
+      </c>
+      <c r="B18" s="9">
+        <v>0.35</v>
+      </c>
+      <c r="C18" s="8" t="s">
+        <v>57</v>
+      </c>
+    </row>
+    <row r="19" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A19" s="10" t="s">
         <v>62</v>
       </c>
-      <c r="B8" s="11" t="s">
-        <v>70</v>
-      </c>
-      <c r="C8" s="10" t="s">
+      <c r="B19" s="11">
+        <v>9</v>
+      </c>
+      <c r="C19" s="10" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="20" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A20" s="10" t="s">
+        <v>64</v>
+      </c>
+      <c r="B20" s="11">
+        <v>11</v>
+      </c>
+      <c r="C20" s="10" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="21" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A21" s="10" t="s">
         <v>65</v>
       </c>
-    </row>
-    <row r="9" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A9" s="10" t="s">
+      <c r="B21" s="11">
+        <v>2</v>
+      </c>
+      <c r="C21" s="10" t="s">
         <v>63</v>
       </c>
-      <c r="B9" s="11" t="s">
+    </row>
+    <row r="22" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A22" s="10" t="s">
+        <v>66</v>
+      </c>
+      <c r="B22" s="11">
+        <v>0.3</v>
+      </c>
+      <c r="C22" s="10" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="23" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A23" s="10" t="s">
+        <v>67</v>
+      </c>
+      <c r="B23" s="11">
+        <v>0.5</v>
+      </c>
+      <c r="C23" s="10" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="24" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A24" s="10" t="s">
         <v>68</v>
       </c>
-      <c r="C9" s="10"/>
-    </row>
-    <row r="10" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A10" s="10" t="s">
-        <v>61</v>
-      </c>
-      <c r="B10" s="11" t="s">
-        <v>69</v>
-      </c>
-      <c r="C10" s="10"/>
-    </row>
-    <row r="11" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A11" s="10" t="s">
-        <v>67</v>
-      </c>
-      <c r="B11" s="11"/>
-      <c r="C11" s="10"/>
-    </row>
-    <row r="12" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A12" s="10" t="s">
-        <v>66</v>
-      </c>
-      <c r="B12" s="11" t="s">
-        <v>71</v>
-      </c>
-      <c r="C12" s="10" t="s">
-        <v>53</v>
-      </c>
-    </row>
-    <row r="13" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A13" s="5" t="s">
-        <v>50</v>
-      </c>
-      <c r="B13" s="8">
-        <v>1</v>
-      </c>
-      <c r="C13" s="5" t="s">
-        <v>48</v>
-      </c>
-    </row>
-    <row r="14" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A14" s="5" t="s">
-        <v>49</v>
-      </c>
-      <c r="B14" s="8">
-        <v>13</v>
-      </c>
-      <c r="C14" s="5" t="s">
-        <v>48</v>
-      </c>
-    </row>
-    <row r="15" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A15" s="5" t="s">
-        <v>56</v>
-      </c>
-      <c r="B15" s="8">
-        <v>2</v>
-      </c>
-      <c r="C15" s="5" t="s">
-        <v>48</v>
-      </c>
-    </row>
-    <row r="16" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A16" s="5" t="s">
-        <v>51</v>
-      </c>
-      <c r="B16" s="8">
-        <v>-0.35</v>
-      </c>
-      <c r="C16" s="5" t="s">
-        <v>48</v>
-      </c>
-    </row>
-    <row r="17" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A17" s="5" t="s">
-        <v>52</v>
-      </c>
-      <c r="B17" s="8">
-        <v>0.35</v>
-      </c>
-      <c r="C17" s="5" t="s">
-        <v>48</v>
-      </c>
-    </row>
-    <row r="18" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A18" s="6" t="s">
-        <v>54</v>
-      </c>
-      <c r="B18" s="9">
-        <v>9</v>
-      </c>
-      <c r="C18" s="6" t="s">
-        <v>64</v>
-      </c>
-    </row>
-    <row r="19" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A19" s="6" t="s">
-        <v>55</v>
-      </c>
-      <c r="B19" s="9">
-        <v>11</v>
-      </c>
-      <c r="C19" s="6" t="s">
-        <v>64</v>
-      </c>
-    </row>
-    <row r="20" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A20" s="6" t="s">
-        <v>57</v>
-      </c>
-      <c r="B20" s="9">
-        <v>2</v>
-      </c>
-      <c r="C20" s="6" t="s">
-        <v>64</v>
-      </c>
-    </row>
-    <row r="21" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A21" s="6" t="s">
-        <v>58</v>
-      </c>
-      <c r="B21" s="9">
-        <v>0.3</v>
-      </c>
-      <c r="C21" s="6" t="s">
-        <v>64</v>
-      </c>
-    </row>
-    <row r="22" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A22" s="6" t="s">
-        <v>59</v>
-      </c>
-      <c r="B22" s="9">
-        <v>0.5</v>
-      </c>
-      <c r="C22" s="6" t="s">
-        <v>64</v>
-      </c>
-    </row>
-    <row r="23" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A23" s="6" t="s">
-        <v>60</v>
-      </c>
-      <c r="B23" s="9">
+      <c r="B24" s="11">
         <v>0.1</v>
       </c>
-      <c r="C23" s="6" t="s">
-        <v>64</v>
+      <c r="C24" s="10" t="s">
+        <v>63</v>
       </c>
     </row>
   </sheetData>
@@ -1577,13 +1648,13 @@
   <sheetData>
     <row r="1" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A1" s="4" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="B1" s="4" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="C1" s="4" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
     </row>
     <row r="2" spans="1:4" x14ac:dyDescent="0.3">
@@ -1913,6 +1984,154 @@
     </row>
     <row r="102" spans="2:2" x14ac:dyDescent="0.3">
       <c r="B102" s="3"/>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{0D99AD71-E642-4142-B8FC-7D196FA946CB}">
+  <dimension ref="A1:C13"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <cols>
+    <col min="1" max="1" width="17.77734375" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="26.6640625" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A1" t="s">
+        <v>7</v>
+      </c>
+      <c r="B1" t="s">
+        <v>8</v>
+      </c>
+      <c r="C1" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="2" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A2" t="s">
+        <v>71</v>
+      </c>
+      <c r="B2">
+        <v>42</v>
+      </c>
+      <c r="C2" t="s">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="3" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A3" t="s">
+        <v>72</v>
+      </c>
+      <c r="B3">
+        <v>100</v>
+      </c>
+      <c r="C3" t="s">
+        <v>81</v>
+      </c>
+    </row>
+    <row r="4" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A4" t="s">
+        <v>73</v>
+      </c>
+      <c r="B4">
+        <v>500</v>
+      </c>
+      <c r="C4" t="s">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="5" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A5" t="s">
+        <v>74</v>
+      </c>
+      <c r="B5">
+        <v>600</v>
+      </c>
+      <c r="C5" t="s">
+        <v>83</v>
+      </c>
+    </row>
+    <row r="6" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A6" t="s">
+        <v>75</v>
+      </c>
+      <c r="B6">
+        <v>0.5</v>
+      </c>
+      <c r="C6" t="s">
+        <v>84</v>
+      </c>
+    </row>
+    <row r="7" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A7" t="s">
+        <v>76</v>
+      </c>
+      <c r="B7">
+        <v>0.9</v>
+      </c>
+      <c r="C7" t="s">
+        <v>85</v>
+      </c>
+    </row>
+    <row r="8" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A8" t="s">
+        <v>77</v>
+      </c>
+      <c r="B8">
+        <v>0.2</v>
+      </c>
+      <c r="C8" t="s">
+        <v>86</v>
+      </c>
+    </row>
+    <row r="9" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A9" t="s">
+        <v>78</v>
+      </c>
+      <c r="B9">
+        <v>0.2</v>
+      </c>
+      <c r="C9" s="12" t="s">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="10" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A10" t="s">
+        <v>79</v>
+      </c>
+      <c r="B10">
+        <v>0.2</v>
+      </c>
+      <c r="C10" s="12" t="s">
+        <v>88</v>
+      </c>
+    </row>
+    <row r="11" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A11" t="s">
+        <v>89</v>
+      </c>
+      <c r="B11">
+        <v>0.2</v>
+      </c>
+    </row>
+    <row r="12" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A12" t="s">
+        <v>90</v>
+      </c>
+      <c r="B12">
+        <v>0.2</v>
+      </c>
+    </row>
+    <row r="13" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A13" t="s">
+        <v>91</v>
+      </c>
+      <c r="B13">
+        <v>0.5</v>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/inputs/inputs_to_load.xlsx
+++ b/inputs/inputs_to_load.xlsx
@@ -3,7 +3,7 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
   <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="20417"/>
   <workbookPr filterPrivacy="1"/>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F66893B6-18EB-44EF-B1D6-AE9515CB1517}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F55436D1-DA22-47C5-9BD3-23E7127946CA}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="0" windowWidth="23040" windowHeight="8076" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -301,7 +301,7 @@
     <t>stall_ratio</t>
   </si>
   <si>
-    <t>mip</t>
+    <t>astar</t>
   </si>
 </sst>
 </file>
@@ -682,12 +682,16 @@
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="7.5546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="2" max="3" width="11.77734375" style="1" bestFit="1" customWidth="1"/>
+    <col min="2" max="3" width="11.6640625" style="1" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="18.109375" style="1" bestFit="1" customWidth="1"/>
     <col min="5" max="5" width="21.109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="19.77734375" style="1" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="19.6640625" style="1" bestFit="1" customWidth="1"/>
     <col min="7" max="7" width="10.6640625" style="1" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="15.77734375" style="1" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="15.6640625" style="1" bestFit="1" customWidth="1"/>
+    <col min="9" max="10" width="12" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="11" bestFit="1" customWidth="1"/>
+    <col min="12" max="14" width="12" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="11" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:8" x14ac:dyDescent="0.3">
@@ -1643,7 +1647,7 @@
   <cols>
     <col min="1" max="1" width="10.33203125" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="18.33203125" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="19.21875" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="19.33203125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:4" x14ac:dyDescent="0.3">
@@ -1661,8 +1665,9 @@
       <c r="A2">
         <v>1</v>
       </c>
-      <c r="B2" s="3">
-        <v>0.33</v>
+      <c r="B2">
+        <f>1/3</f>
+        <v>0.33333333333333331</v>
       </c>
       <c r="C2">
         <v>-0.5</v>
@@ -1672,8 +1677,9 @@
       <c r="A3">
         <v>2</v>
       </c>
-      <c r="B3" s="3">
-        <v>0.33</v>
+      <c r="B3">
+        <f>1/3</f>
+        <v>0.33333333333333331</v>
       </c>
       <c r="C3">
         <v>0</v>
@@ -1683,8 +1689,9 @@
       <c r="A4">
         <v>3</v>
       </c>
-      <c r="B4" s="3">
-        <v>0.33</v>
+      <c r="B4">
+        <f>1/3</f>
+        <v>0.33333333333333331</v>
       </c>
       <c r="C4">
         <v>0.5</v>
@@ -1995,7 +2002,7 @@
   <dimension ref="A1:C13"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="17.77734375" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="17.6640625" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="26.6640625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
@@ -2026,7 +2033,7 @@
         <v>72</v>
       </c>
       <c r="B3">
-        <v>100</v>
+        <v>50</v>
       </c>
       <c r="C3" t="s">
         <v>81</v>
@@ -2037,7 +2044,7 @@
         <v>73</v>
       </c>
       <c r="B4">
-        <v>500</v>
+        <v>250</v>
       </c>
       <c r="C4" t="s">
         <v>82</v>
@@ -2130,7 +2137,7 @@
         <v>91</v>
       </c>
       <c r="B13">
-        <v>0.5</v>
+        <v>0.2</v>
       </c>
     </row>
   </sheetData>
